--- a/sql.xlsx
+++ b/sql.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\Load_testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="1">
   <si>
     <t>select * from `users`;</t>
   </si>
@@ -345,7 +345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -368,11 +368,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
